--- a/final_data_pipeline/output/311411_elec_options.xlsx
+++ b/final_data_pipeline/output/311411_elec_options.xlsx
@@ -915,7 +915,7 @@
         <v>116</v>
       </c>
       <c r="AD2">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE2">
         <v>8000</v>
@@ -1007,7 +1007,7 @@
         <v>116</v>
       </c>
       <c r="AD3">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE3">
         <v>8000</v>
@@ -1096,7 +1096,7 @@
         <v>116</v>
       </c>
       <c r="AD4">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE4">
         <v>8000</v>
@@ -1185,7 +1185,7 @@
         <v>116</v>
       </c>
       <c r="AD5">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE5">
         <v>8000</v>
@@ -5223,7 +5223,7 @@
         <v>116</v>
       </c>
       <c r="AD50">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE50">
         <v>8000</v>
@@ -5315,7 +5315,7 @@
         <v>116</v>
       </c>
       <c r="AD51">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE51">
         <v>8000</v>
@@ -5404,7 +5404,7 @@
         <v>116</v>
       </c>
       <c r="AD52">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE52">
         <v>8000</v>
@@ -5493,7 +5493,7 @@
         <v>116</v>
       </c>
       <c r="AD53">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE53">
         <v>8000</v>
@@ -5585,7 +5585,7 @@
         <v>116</v>
       </c>
       <c r="AD54">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE54">
         <v>8000</v>
@@ -5674,7 +5674,7 @@
         <v>116</v>
       </c>
       <c r="AD55">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE55">
         <v>8000</v>
@@ -5763,7 +5763,7 @@
         <v>116</v>
       </c>
       <c r="AD56">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE56">
         <v>8000</v>
@@ -5852,7 +5852,7 @@
         <v>116</v>
       </c>
       <c r="AD57">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE57">
         <v>8000</v>
@@ -5944,7 +5944,7 @@
         <v>116</v>
       </c>
       <c r="AD58">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE58">
         <v>8000</v>
@@ -6039,7 +6039,7 @@
         <v>116</v>
       </c>
       <c r="AD59">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE59">
         <v>8000</v>
@@ -6137,7 +6137,7 @@
         <v>116</v>
       </c>
       <c r="AD60">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE60">
         <v>8000</v>
@@ -6235,7 +6235,7 @@
         <v>116</v>
       </c>
       <c r="AD61">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE61">
         <v>8000</v>
@@ -6333,7 +6333,7 @@
         <v>116</v>
       </c>
       <c r="AD62">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE62">
         <v>8000</v>
@@ -6431,7 +6431,7 @@
         <v>116</v>
       </c>
       <c r="AD63">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE63">
         <v>8000</v>
@@ -6529,7 +6529,7 @@
         <v>116</v>
       </c>
       <c r="AD64">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE64">
         <v>8000</v>
@@ -6627,7 +6627,7 @@
         <v>116</v>
       </c>
       <c r="AD65">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE65">
         <v>8000</v>
@@ -6725,7 +6725,7 @@
         <v>116</v>
       </c>
       <c r="AD66">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE66">
         <v>8000</v>
@@ -6820,7 +6820,7 @@
         <v>116</v>
       </c>
       <c r="AD67">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE67">
         <v>8000</v>
@@ -6915,7 +6915,7 @@
         <v>116</v>
       </c>
       <c r="AD68">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE68">
         <v>8000</v>
@@ -7010,7 +7010,7 @@
         <v>116</v>
       </c>
       <c r="AD69">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE69">
         <v>8000</v>
@@ -7105,7 +7105,7 @@
         <v>116</v>
       </c>
       <c r="AD70">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE70">
         <v>8000</v>
@@ -7194,7 +7194,7 @@
         <v>116</v>
       </c>
       <c r="AD71">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE71">
         <v>8000</v>
@@ -7289,7 +7289,7 @@
         <v>116</v>
       </c>
       <c r="AD72">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE72">
         <v>8000</v>
@@ -7384,7 +7384,7 @@
         <v>116</v>
       </c>
       <c r="AD73">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE73">
         <v>8000</v>
@@ -7479,7 +7479,7 @@
         <v>116</v>
       </c>
       <c r="AD74">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE74">
         <v>8000</v>
@@ -7568,7 +7568,7 @@
         <v>116</v>
       </c>
       <c r="AD75">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE75">
         <v>8000</v>
@@ -7663,7 +7663,7 @@
         <v>116</v>
       </c>
       <c r="AD76">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE76">
         <v>8000</v>
@@ -7758,7 +7758,7 @@
         <v>116</v>
       </c>
       <c r="AD77">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE77">
         <v>8000</v>
@@ -7853,7 +7853,7 @@
         <v>116</v>
       </c>
       <c r="AD78">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE78">
         <v>8000</v>
@@ -7948,7 +7948,7 @@
         <v>116</v>
       </c>
       <c r="AD79">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE79">
         <v>8000</v>
@@ -8043,7 +8043,7 @@
         <v>116</v>
       </c>
       <c r="AD80">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE80">
         <v>8000</v>
@@ -8138,7 +8138,7 @@
         <v>116</v>
       </c>
       <c r="AD81">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE81">
         <v>8000</v>
@@ -8233,7 +8233,7 @@
         <v>116</v>
       </c>
       <c r="AD82">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE82">
         <v>8000</v>
@@ -8328,7 +8328,7 @@
         <v>116</v>
       </c>
       <c r="AD83">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE83">
         <v>8000</v>
@@ -8423,7 +8423,7 @@
         <v>116</v>
       </c>
       <c r="AD84">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE84">
         <v>8000</v>
@@ -8518,7 +8518,7 @@
         <v>116</v>
       </c>
       <c r="AD85">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE85">
         <v>8000</v>
@@ -8613,7 +8613,7 @@
         <v>116</v>
       </c>
       <c r="AD86">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE86">
         <v>8000</v>
@@ -8708,7 +8708,7 @@
         <v>116</v>
       </c>
       <c r="AD87">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE87">
         <v>8000</v>
@@ -8797,7 +8797,7 @@
         <v>116</v>
       </c>
       <c r="AD88">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE88">
         <v>8000</v>
@@ -8892,7 +8892,7 @@
         <v>116</v>
       </c>
       <c r="AD89">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE89">
         <v>8000</v>
@@ -8981,7 +8981,7 @@
         <v>116</v>
       </c>
       <c r="AD90">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="AE90">
         <v>8000</v>
@@ -9076,7 +9076,7 @@
         <v>116</v>
       </c>
       <c r="AD91">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="AE91">
         <v>8000</v>
@@ -9165,7 +9165,7 @@
         <v>116</v>
       </c>
       <c r="AD92">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="AE92">
         <v>8000</v>
@@ -9254,7 +9254,7 @@
         <v>116</v>
       </c>
       <c r="AD93">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="AE93">
         <v>8000</v>
@@ -9343,7 +9343,7 @@
         <v>116</v>
       </c>
       <c r="AD94">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="AE94">
         <v>8000</v>
@@ -9432,7 +9432,7 @@
         <v>116</v>
       </c>
       <c r="AD95">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="AE95">
         <v>8000</v>
@@ -9521,7 +9521,7 @@
         <v>116</v>
       </c>
       <c r="AD96">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="AE96">
         <v>8000</v>
@@ -9613,7 +9613,7 @@
         <v>116</v>
       </c>
       <c r="AD97">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="AE97">
         <v>8000</v>
@@ -9702,7 +9702,7 @@
         <v>116</v>
       </c>
       <c r="AD98">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="AE98">
         <v>8000</v>
@@ -9794,7 +9794,7 @@
         <v>116</v>
       </c>
       <c r="AD99">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="AE99">
         <v>8000</v>
@@ -9895,7 +9895,7 @@
         <v>116</v>
       </c>
       <c r="AD100">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="AE100">
         <v>8000</v>
@@ -9984,7 +9984,7 @@
         <v>116</v>
       </c>
       <c r="AD101">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="AE101">
         <v>8000</v>
@@ -10079,7 +10079,7 @@
         <v>116</v>
       </c>
       <c r="AD102">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="AE102">
         <v>8000</v>
@@ -10174,7 +10174,7 @@
         <v>116</v>
       </c>
       <c r="AD103">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="AE103">
         <v>8000</v>
@@ -10263,7 +10263,7 @@
         <v>116</v>
       </c>
       <c r="AD104">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="AE104">
         <v>8000</v>
@@ -10361,7 +10361,7 @@
         <v>116</v>
       </c>
       <c r="AD105">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="AE105">
         <v>8000</v>
@@ -10453,7 +10453,7 @@
         <v>116</v>
       </c>
       <c r="AD106">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="AE106">
         <v>8000</v>
@@ -11649,7 +11649,7 @@
         <v>116</v>
       </c>
       <c r="AD119">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE119">
         <v>8000</v>
@@ -11738,7 +11738,7 @@
         <v>116</v>
       </c>
       <c r="AD120">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE120">
         <v>8000</v>
@@ -11830,7 +11830,7 @@
         <v>116</v>
       </c>
       <c r="AD121">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE121">
         <v>8000</v>
@@ -11919,7 +11919,7 @@
         <v>116</v>
       </c>
       <c r="AD122">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE122">
         <v>8000</v>
@@ -12017,7 +12017,7 @@
         <v>116</v>
       </c>
       <c r="AD123">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE123">
         <v>8000</v>
@@ -12106,7 +12106,7 @@
         <v>116</v>
       </c>
       <c r="AD124">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE124">
         <v>8000</v>
@@ -12201,7 +12201,7 @@
         <v>116</v>
       </c>
       <c r="AD125">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE125">
         <v>8000</v>
@@ -12293,7 +12293,7 @@
         <v>116</v>
       </c>
       <c r="AD126">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE126">
         <v>8000</v>
@@ -12382,7 +12382,7 @@
         <v>116</v>
       </c>
       <c r="AD127">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE127">
         <v>8000</v>
@@ -12471,7 +12471,7 @@
         <v>116</v>
       </c>
       <c r="AD128">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE128">
         <v>8000</v>
@@ -12560,7 +12560,7 @@
         <v>116</v>
       </c>
       <c r="AD129">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE129">
         <v>8000</v>
@@ -12655,7 +12655,7 @@
         <v>116</v>
       </c>
       <c r="AD130">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE130">
         <v>8000</v>
@@ -16792,7 +16792,7 @@
         <v>116</v>
       </c>
       <c r="AD175">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE175">
         <v>8000</v>
@@ -16881,7 +16881,7 @@
         <v>116</v>
       </c>
       <c r="AD176">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE176">
         <v>8000</v>
@@ -16970,7 +16970,7 @@
         <v>116</v>
       </c>
       <c r="AD177">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE177">
         <v>8000</v>
@@ -17062,7 +17062,7 @@
         <v>116</v>
       </c>
       <c r="AD178">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE178">
         <v>8000</v>
@@ -17151,7 +17151,7 @@
         <v>116</v>
       </c>
       <c r="AD179">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE179">
         <v>8000</v>
@@ -17240,7 +17240,7 @@
         <v>116</v>
       </c>
       <c r="AD180">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE180">
         <v>8000</v>
@@ -17329,7 +17329,7 @@
         <v>116</v>
       </c>
       <c r="AD181">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE181">
         <v>8000</v>
@@ -17418,7 +17418,7 @@
         <v>116</v>
       </c>
       <c r="AD182">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE182">
         <v>8000</v>
@@ -17513,7 +17513,7 @@
         <v>116</v>
       </c>
       <c r="AD183">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE183">
         <v>8000</v>
@@ -17608,7 +17608,7 @@
         <v>116</v>
       </c>
       <c r="AD184">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE184">
         <v>8000</v>
@@ -17703,7 +17703,7 @@
         <v>116</v>
       </c>
       <c r="AD185">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE185">
         <v>8000</v>
@@ -17798,7 +17798,7 @@
         <v>116</v>
       </c>
       <c r="AD186">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE186">
         <v>8000</v>
@@ -17893,7 +17893,7 @@
         <v>116</v>
       </c>
       <c r="AD187">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE187">
         <v>8000</v>
@@ -17982,7 +17982,7 @@
         <v>116</v>
       </c>
       <c r="AD188">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE188">
         <v>8000</v>
@@ -18080,7 +18080,7 @@
         <v>116</v>
       </c>
       <c r="AD189">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE189">
         <v>8000</v>
@@ -18178,7 +18178,7 @@
         <v>116</v>
       </c>
       <c r="AD190">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE190">
         <v>8000</v>
@@ -18270,7 +18270,7 @@
         <v>116</v>
       </c>
       <c r="AD191">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE191">
         <v>8000</v>
@@ -18368,7 +18368,7 @@
         <v>116</v>
       </c>
       <c r="AD192">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE192">
         <v>8000</v>
@@ -18457,7 +18457,7 @@
         <v>116</v>
       </c>
       <c r="AD193">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE193">
         <v>8000</v>
@@ -18552,7 +18552,7 @@
         <v>116</v>
       </c>
       <c r="AD194">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE194">
         <v>8000</v>
@@ -18647,7 +18647,7 @@
         <v>116</v>
       </c>
       <c r="AD195">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE195">
         <v>8000</v>
@@ -18742,7 +18742,7 @@
         <v>116</v>
       </c>
       <c r="AD196">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE196">
         <v>8000</v>
@@ -18837,7 +18837,7 @@
         <v>116</v>
       </c>
       <c r="AD197">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE197">
         <v>8000</v>
@@ -18932,7 +18932,7 @@
         <v>116</v>
       </c>
       <c r="AD198">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE198">
         <v>8000</v>
@@ -19027,7 +19027,7 @@
         <v>116</v>
       </c>
       <c r="AD199">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE199">
         <v>8000</v>
@@ -19125,7 +19125,7 @@
         <v>116</v>
       </c>
       <c r="AD200">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE200">
         <v>8000</v>
@@ -19220,7 +19220,7 @@
         <v>116</v>
       </c>
       <c r="AD201">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE201">
         <v>8000</v>
@@ -19315,7 +19315,7 @@
         <v>116</v>
       </c>
       <c r="AD202">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE202">
         <v>8000</v>
@@ -19410,7 +19410,7 @@
         <v>116</v>
       </c>
       <c r="AD203">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE203">
         <v>8000</v>
@@ -19499,7 +19499,7 @@
         <v>116</v>
       </c>
       <c r="AD204">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE204">
         <v>8000</v>
@@ -19594,7 +19594,7 @@
         <v>116</v>
       </c>
       <c r="AD205">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE205">
         <v>8000</v>
@@ -19692,7 +19692,7 @@
         <v>116</v>
       </c>
       <c r="AD206">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE206">
         <v>8000</v>
